--- a/uploads/res-region.xlsx
+++ b/uploads/res-region.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\fproject\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE6CA0E6-E4F8-4A50-BA11-F59FEFD5F8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83352F36-2CB6-410B-BE14-0B4749771655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15840" xr2:uid="{BFD3F507-F06E-42AD-B815-7379EFEE9CE0}"/>
   </bookViews>
@@ -34,15 +34,579 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>id_res_region</t>
-  </si>
-  <si>
-    <t>id_res</t>
-  </si>
-  <si>
-    <t>id_region</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="191">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Алтайского края</t>
+  </si>
+  <si>
+    <t>Алтайский край</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Амурской области</t>
+  </si>
+  <si>
+    <t>Амурская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Архангельской области</t>
+  </si>
+  <si>
+    <t>Архангельская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Архангельской области и Ненецкого автономного округа</t>
+  </si>
+  <si>
+    <t>Ненецкий автономный округ</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Астраханской области</t>
+  </si>
+  <si>
+    <t>Астраханская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Белгородской области</t>
+  </si>
+  <si>
+    <t>Белгородская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Брянской области</t>
+  </si>
+  <si>
+    <t>Брянская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Владимирской области</t>
+  </si>
+  <si>
+    <t>Владимирская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Волгоградской области</t>
+  </si>
+  <si>
+    <t>Волгоградская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Вологодской области</t>
+  </si>
+  <si>
+    <t>Вологодская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Воронежской области</t>
+  </si>
+  <si>
+    <t>Воронежская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система г. Москвы</t>
+  </si>
+  <si>
+    <t>Москва</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система г. Москвы и Московской области</t>
+  </si>
+  <si>
+    <t>Московская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система г. Санкт-Петербурга</t>
+  </si>
+  <si>
+    <t>Санкт-Петербург</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система г. Санкт-Петербурга и Ленинградской области</t>
+  </si>
+  <si>
+    <t>Ленинградская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система г. Севастополь</t>
+  </si>
+  <si>
+    <t>Севастополь</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Донецкой Народной Республики</t>
+  </si>
+  <si>
+    <t>Донецкая Народная Республика</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Еврейской автономной области</t>
+  </si>
+  <si>
+    <t>Еврейская автономная область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Забайкальского края</t>
+  </si>
+  <si>
+    <t>Забайкальский край</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Запорожской области</t>
+  </si>
+  <si>
+    <t>Запорожская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Ивановской области</t>
+  </si>
+  <si>
+    <t>Ивановская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Иркутской области</t>
+  </si>
+  <si>
+    <t>Иркутская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Кабардино-Балкарской Республики</t>
+  </si>
+  <si>
+    <t>Кабардино-Балкарская Республика</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Калининградской области</t>
+  </si>
+  <si>
+    <t>Калининградская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Калужской области</t>
+  </si>
+  <si>
+    <t>Калужская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Камчатского края</t>
+  </si>
+  <si>
+    <t>Камчатский край</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Карачаево-Черкесской Республики</t>
+  </si>
+  <si>
+    <t>Карачаево-Черкесская Республика</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Кемеровской области - Кузбасса</t>
+  </si>
+  <si>
+    <t>Кемеровская область - Кузбасс</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Кировской области</t>
+  </si>
+  <si>
+    <t>Кировская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Костромской области</t>
+  </si>
+  <si>
+    <t>Костромская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Краснодарского края</t>
+  </si>
+  <si>
+    <t>Краснодарский край</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Краснодарского края и Республики Адыгея</t>
+  </si>
+  <si>
+    <t>Республика Адыгея</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Красноярского края</t>
+  </si>
+  <si>
+    <t>Красноярский край</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Красноярского края и Республики Тыва</t>
+  </si>
+  <si>
+    <t>Республика Тыва</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Курганской области</t>
+  </si>
+  <si>
+    <t>Курганская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Курской области</t>
+  </si>
+  <si>
+    <t>Курская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Ленинградской области</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Липецкой области</t>
+  </si>
+  <si>
+    <t>Липецкая область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Луганской Народной Республики</t>
+  </si>
+  <si>
+    <t>Луганская Народная Республика</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Магаданской области</t>
+  </si>
+  <si>
+    <t>Магаданская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Московской области</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Мурманской области</t>
+  </si>
+  <si>
+    <t>Мурманская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Ненецкого автономного округа</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Нижегородской области</t>
+  </si>
+  <si>
+    <t>Нижегородская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Новгородской области</t>
+  </si>
+  <si>
+    <t>Новгородская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Новосибирской области</t>
+  </si>
+  <si>
+    <t>Новосибирская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Омской области</t>
+  </si>
+  <si>
+    <t>Омская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Оренбургской области</t>
+  </si>
+  <si>
+    <t>Оренбургская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Орловской области</t>
+  </si>
+  <si>
+    <t>Орловская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Пензенской области</t>
+  </si>
+  <si>
+    <t>Пензенская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Пермского края</t>
+  </si>
+  <si>
+    <t>Пермский край</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Приморского края</t>
+  </si>
+  <si>
+    <t>Приморский край</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Псковской области</t>
+  </si>
+  <si>
+    <t>Псковская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Адыгея</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Алтай</t>
+  </si>
+  <si>
+    <t>Республика Алтай</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Алтай и Алтайского края</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Башкортостан</t>
+  </si>
+  <si>
+    <t>Республика Башкортостан</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Бурятия</t>
+  </si>
+  <si>
+    <t>Республика Бурятия</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Дагестан</t>
+  </si>
+  <si>
+    <t>Республика Дагестан</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Ингушетия</t>
+  </si>
+  <si>
+    <t>Республика Ингушетия</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Калмыкия</t>
+  </si>
+  <si>
+    <t>Республика Калмыкия</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Карелия</t>
+  </si>
+  <si>
+    <t>Республика Карелия</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Коми</t>
+  </si>
+  <si>
+    <t>Республика Коми</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Крым</t>
+  </si>
+  <si>
+    <t>Республика Крым</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Крым и г. Севастополя</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Марий Эл</t>
+  </si>
+  <si>
+    <t>Республика Марий Эл</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Мордовия</t>
+  </si>
+  <si>
+    <t>Республика Мордовия</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Саха (Якутия)</t>
+  </si>
+  <si>
+    <t>Республика Саха (Якутия)</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Северная Осетия - Алания</t>
+  </si>
+  <si>
+    <t>Республика Северная Осетия - Алания</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Татарстан</t>
+  </si>
+  <si>
+    <t>Республика Татарстан</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Тыва</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Республики Хакасия</t>
+  </si>
+  <si>
+    <t>Республика Хакасия</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Ростовской области</t>
+  </si>
+  <si>
+    <t>Ростовская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Рязанской области</t>
+  </si>
+  <si>
+    <t>Рязанская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Самарской области</t>
+  </si>
+  <si>
+    <t>Самарская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Саратовской области</t>
+  </si>
+  <si>
+    <t>Саратовская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Сахалинской области</t>
+  </si>
+  <si>
+    <t>Сахалинская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Свердловской области</t>
+  </si>
+  <si>
+    <t>Свердловская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Смоленской области</t>
+  </si>
+  <si>
+    <t>Смоленская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Ставропольского края</t>
+  </si>
+  <si>
+    <t>Ставропольский край</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Таймырского Долгано-Ненецкого муниципального района, Туруханского района и городского округа г. Норильск Красноярского края</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Тамбовской области</t>
+  </si>
+  <si>
+    <t>Тамбовская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Тверской области</t>
+  </si>
+  <si>
+    <t>Тверская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Томской области</t>
+  </si>
+  <si>
+    <t>Томская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Тульской области</t>
+  </si>
+  <si>
+    <t>Тульская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Тюменской области</t>
+  </si>
+  <si>
+    <t>Тюменская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Тюменской области, ХМАО и ЯНАО</t>
+  </si>
+  <si>
+    <t>Ханты-Мансийский автономный округ - Югра</t>
+  </si>
+  <si>
+    <t>Ямало-Ненецкий автономный округ</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Удмуртской Республики</t>
+  </si>
+  <si>
+    <t>Удмуртская Республика</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Ульяновской области</t>
+  </si>
+  <si>
+    <t>Ульяновская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Хабаровского края</t>
+  </si>
+  <si>
+    <t>Хабаровский край</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Хабаровского края и Еврейской автономной области</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Херсонской области</t>
+  </si>
+  <si>
+    <t>Херсонская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система ХМАО</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Челябинской области</t>
+  </si>
+  <si>
+    <t>Челябинская область</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Чеченской Республики</t>
+  </si>
+  <si>
+    <t>Чеченская Республика</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Чувашской Республики</t>
+  </si>
+  <si>
+    <t>Чувашская Республика</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Чукотского автономного округа</t>
+  </si>
+  <si>
+    <t>Чукотский автономный округ</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система ЯНАО</t>
+  </si>
+  <si>
+    <t>Электроэнергетическая система Ярославской области</t>
+  </si>
+  <si>
+    <t>Ярославская область</t>
+  </si>
+  <si>
+    <t>regional_energy_system</t>
+  </si>
+  <si>
+    <t>regional_district</t>
   </si>
 </sst>
 </file>
@@ -88,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +662,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -417,6 +984,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -424,1209 +993,1209 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>189</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2">
-        <v>1</v>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2</v>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2">
-        <v>3</v>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2">
-        <v>3</v>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2">
-        <v>36</v>
+      <c r="B6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>4</v>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2">
-        <v>5</v>
+      <c r="B8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2">
-        <v>6</v>
+      <c r="B9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2">
-        <v>7</v>
+      <c r="B10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
-        <v>9</v>
-      </c>
-      <c r="C11" s="2">
-        <v>8</v>
+      <c r="B11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
-        <v>10</v>
-      </c>
-      <c r="C12" s="2">
-        <v>9</v>
+      <c r="B12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
-        <v>11</v>
-      </c>
-      <c r="C13" s="2">
-        <v>10</v>
+      <c r="B13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2">
-        <v>33</v>
+      <c r="B14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
-        <v>13</v>
-      </c>
-      <c r="C15" s="2">
-        <v>33</v>
+      <c r="B15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
-        <v>13</v>
-      </c>
-      <c r="C16" s="2">
-        <v>34</v>
+      <c r="B16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
-        <v>14</v>
-      </c>
-      <c r="C17" s="2">
-        <v>67</v>
+      <c r="B17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2">
-        <v>67</v>
+      <c r="B18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="B19" s="4" t="s">
         <v>29</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2">
-        <v>71</v>
+      <c r="B20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
-        <v>17</v>
-      </c>
-      <c r="C21" s="2">
-        <v>11</v>
+      <c r="B21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
-        <v>18</v>
-      </c>
-      <c r="C22" s="2">
-        <v>12</v>
+      <c r="B22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
-        <v>19</v>
-      </c>
-      <c r="C23" s="2">
-        <v>13</v>
+      <c r="B23" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
-        <v>20</v>
-      </c>
-      <c r="C24" s="2">
-        <v>14</v>
+      <c r="B24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
-        <v>21</v>
-      </c>
-      <c r="C25" s="2">
-        <v>15</v>
+      <c r="B25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
-        <v>22</v>
-      </c>
-      <c r="C26" s="2">
-        <v>16</v>
+      <c r="B26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="2">
-        <v>23</v>
-      </c>
-      <c r="C27" s="2">
-        <v>17</v>
+      <c r="B27" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="2">
-        <v>24</v>
-      </c>
-      <c r="C28" s="2">
-        <v>18</v>
+      <c r="B28" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="2">
-        <v>25</v>
-      </c>
-      <c r="C29" s="2">
-        <v>19</v>
+      <c r="B29" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="2">
-        <v>26</v>
-      </c>
-      <c r="C30" s="2">
-        <v>20</v>
+      <c r="B30" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="2">
-        <v>27</v>
-      </c>
-      <c r="C31" s="2">
-        <v>21</v>
+      <c r="B31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="2">
-        <v>28</v>
-      </c>
-      <c r="C32" s="2">
-        <v>22</v>
+      <c r="B32" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" s="2">
-        <v>29</v>
-      </c>
-      <c r="C33" s="2">
-        <v>23</v>
+      <c r="B33" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" s="2">
-        <v>30</v>
-      </c>
-      <c r="C34" s="2">
-        <v>24</v>
+      <c r="B34" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="B35" s="2">
-        <v>31</v>
-      </c>
-      <c r="C35" s="2">
-        <v>25</v>
+      <c r="B35" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="2">
-        <v>32</v>
-      </c>
-      <c r="C36" s="2">
-        <v>25</v>
+      <c r="B36" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="2">
-        <v>32</v>
-      </c>
-      <c r="C37" s="2">
-        <v>47</v>
+      <c r="B37" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="2">
-        <v>33</v>
-      </c>
-      <c r="C38" s="2">
-        <v>26</v>
+      <c r="B38" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="2">
-        <v>34</v>
-      </c>
-      <c r="C39" s="2">
-        <v>26</v>
+      <c r="B39" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" s="2">
-        <v>34</v>
-      </c>
-      <c r="C40" s="2">
-        <v>62</v>
+      <c r="B40" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
-      <c r="B41" s="2">
-        <v>35</v>
-      </c>
-      <c r="C41" s="2">
-        <v>27</v>
+      <c r="B41" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" s="2">
-        <v>36</v>
-      </c>
-      <c r="C42" s="2">
-        <v>28</v>
+      <c r="B42" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" s="2">
-        <v>37</v>
-      </c>
-      <c r="C43" s="2">
-        <v>29</v>
+      <c r="B43" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="B44" s="2">
-        <v>38</v>
-      </c>
-      <c r="C44" s="2">
-        <v>30</v>
+      <c r="B44" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
-      <c r="B45" s="2">
-        <v>39</v>
-      </c>
-      <c r="C45" s="2">
-        <v>31</v>
+      <c r="B45" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" s="2">
-        <v>40</v>
-      </c>
-      <c r="C46" s="2">
-        <v>32</v>
+      <c r="B46" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
-      <c r="B47" s="2">
-        <v>41</v>
-      </c>
-      <c r="C47" s="2">
-        <v>34</v>
+      <c r="B47" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="B48" s="2">
-        <v>42</v>
-      </c>
-      <c r="C48" s="2">
-        <v>35</v>
+      <c r="B48" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
-      <c r="B49" s="2">
-        <v>43</v>
-      </c>
-      <c r="C49" s="2">
-        <v>36</v>
+      <c r="B49" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
-      <c r="B50" s="2">
-        <v>44</v>
-      </c>
-      <c r="C50" s="2">
-        <v>37</v>
+      <c r="B50" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
-      <c r="B51" s="2">
-        <v>45</v>
-      </c>
-      <c r="C51" s="2">
-        <v>38</v>
+      <c r="B51" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" s="2">
-        <v>46</v>
-      </c>
-      <c r="C52" s="2">
-        <v>39</v>
+      <c r="B52" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" s="2">
-        <v>47</v>
-      </c>
-      <c r="C53" s="2">
-        <v>40</v>
+      <c r="B53" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" s="2">
-        <v>48</v>
-      </c>
-      <c r="C54" s="2">
-        <v>41</v>
+      <c r="B54" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
-      <c r="B55" s="2">
-        <v>49</v>
-      </c>
-      <c r="C55" s="2">
-        <v>42</v>
+      <c r="B55" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" s="2">
-        <v>50</v>
-      </c>
-      <c r="C56" s="2">
-        <v>43</v>
+      <c r="B56" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" s="2">
-        <v>51</v>
-      </c>
-      <c r="C57" s="2">
-        <v>44</v>
+      <c r="B57" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" s="2">
-        <v>52</v>
-      </c>
-      <c r="C58" s="2">
-        <v>45</v>
+      <c r="B58" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" s="2">
-        <v>53</v>
-      </c>
-      <c r="C59" s="2">
-        <v>46</v>
+      <c r="B59" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" s="2">
-        <v>54</v>
-      </c>
-      <c r="C60" s="2">
-        <v>47</v>
+      <c r="B60" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" s="2">
-        <v>55</v>
-      </c>
-      <c r="C61" s="2">
-        <v>48</v>
+      <c r="B61" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" s="2">
-        <v>56</v>
-      </c>
-      <c r="C62" s="2">
-        <v>48</v>
+      <c r="B62" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="B63" s="2">
-        <v>56</v>
-      </c>
-      <c r="C63" s="2">
-        <v>1</v>
+      <c r="B63" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" s="2">
-        <v>57</v>
-      </c>
-      <c r="C64" s="2">
-        <v>49</v>
+      <c r="B64" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
-      <c r="B65" s="2">
-        <v>58</v>
-      </c>
-      <c r="C65" s="2">
-        <v>50</v>
+      <c r="B65" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
-      <c r="B66" s="2">
-        <v>59</v>
-      </c>
-      <c r="C66" s="2">
-        <v>51</v>
+      <c r="B66" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
-      <c r="B67" s="2">
-        <v>60</v>
-      </c>
-      <c r="C67" s="2">
-        <v>52</v>
+      <c r="B67" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
-      <c r="B68" s="2">
-        <v>61</v>
-      </c>
-      <c r="C68" s="2">
-        <v>53</v>
+      <c r="B68" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
-      <c r="B69" s="2">
-        <v>62</v>
-      </c>
-      <c r="C69" s="2">
-        <v>54</v>
+      <c r="B69" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
-      <c r="B70" s="2">
-        <v>63</v>
-      </c>
-      <c r="C70" s="2">
-        <v>55</v>
+      <c r="B70" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
-      <c r="B71" s="2">
-        <v>64</v>
-      </c>
-      <c r="C71" s="2">
-        <v>56</v>
+      <c r="B71" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
-      <c r="B72" s="2">
-        <v>65</v>
-      </c>
-      <c r="C72" s="2">
-        <v>56</v>
+      <c r="B72" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
-      <c r="B73" s="2">
-        <v>65</v>
-      </c>
-      <c r="C73" s="2">
-        <v>71</v>
+      <c r="B73" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" s="2">
-        <v>66</v>
-      </c>
-      <c r="C74" s="2">
-        <v>57</v>
+      <c r="B74" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
-      <c r="B75" s="2">
-        <v>67</v>
-      </c>
-      <c r="C75" s="2">
-        <v>58</v>
+      <c r="B75" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
-      <c r="B76" s="2">
-        <v>68</v>
-      </c>
-      <c r="C76" s="2">
-        <v>59</v>
+      <c r="B76" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
-      <c r="B77" s="2">
-        <v>69</v>
-      </c>
-      <c r="C77" s="2">
-        <v>60</v>
+      <c r="B77" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
-      <c r="B78" s="2">
-        <v>70</v>
-      </c>
-      <c r="C78" s="2">
-        <v>61</v>
+      <c r="B78" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
-      <c r="B79" s="2">
-        <v>71</v>
-      </c>
-      <c r="C79" s="2">
-        <v>62</v>
+      <c r="B79" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
-      <c r="B80" s="2">
-        <v>72</v>
-      </c>
-      <c r="C80" s="2">
-        <v>63</v>
+      <c r="B80" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
-      <c r="B81" s="2">
-        <v>73</v>
-      </c>
-      <c r="C81" s="2">
-        <v>64</v>
+      <c r="B81" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
-      <c r="B82" s="2">
-        <v>74</v>
-      </c>
-      <c r="C82" s="2">
-        <v>65</v>
+      <c r="B82" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
-      <c r="B83" s="2">
-        <v>75</v>
-      </c>
-      <c r="C83" s="2">
-        <v>66</v>
+      <c r="B83" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
-      <c r="B84" s="2">
-        <v>76</v>
-      </c>
-      <c r="C84" s="2">
-        <v>68</v>
+      <c r="B84" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
-      <c r="B85" s="2">
-        <v>77</v>
-      </c>
-      <c r="C85" s="2">
-        <v>69</v>
+      <c r="B85" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
-      <c r="B86" s="2">
-        <v>78</v>
-      </c>
-      <c r="C86" s="2">
-        <v>70</v>
+      <c r="B86" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
-      <c r="B87" s="2">
-        <v>79</v>
-      </c>
-      <c r="C87" s="2">
-        <v>72</v>
+      <c r="B87" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
-      <c r="B88" s="2">
-        <v>80</v>
-      </c>
-      <c r="C88" s="2">
-        <v>73</v>
+      <c r="B88" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
-      <c r="B89" s="2">
-        <v>81</v>
-      </c>
-      <c r="C89" s="2">
-        <v>26</v>
+      <c r="B89" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
-      <c r="B90" s="2">
-        <v>82</v>
-      </c>
-      <c r="C90" s="2">
-        <v>74</v>
+      <c r="B90" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
-      <c r="B91" s="2">
-        <v>83</v>
-      </c>
-      <c r="C91" s="2">
-        <v>75</v>
+      <c r="B91" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
-      <c r="B92" s="2">
-        <v>84</v>
-      </c>
-      <c r="C92" s="2">
-        <v>76</v>
+      <c r="B92" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>92</v>
       </c>
-      <c r="B93" s="2">
-        <v>85</v>
-      </c>
-      <c r="C93" s="2">
-        <v>77</v>
+      <c r="B93" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>93</v>
       </c>
-      <c r="B94" s="2">
-        <v>86</v>
-      </c>
-      <c r="C94" s="2">
-        <v>78</v>
+      <c r="B94" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>94</v>
       </c>
-      <c r="B95" s="2">
-        <v>87</v>
-      </c>
-      <c r="C95" s="2">
-        <v>78</v>
+      <c r="B95" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>95</v>
       </c>
-      <c r="B96" s="2">
-        <v>87</v>
-      </c>
-      <c r="C96" s="2">
-        <v>82</v>
+      <c r="B96" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
-      <c r="B97" s="2">
-        <v>87</v>
-      </c>
-      <c r="C97" s="2">
-        <v>88</v>
+      <c r="B97" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
-      <c r="B98" s="2">
-        <v>88</v>
-      </c>
-      <c r="C98" s="2">
-        <v>79</v>
+      <c r="B98" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>98</v>
       </c>
-      <c r="B99" s="2">
-        <v>89</v>
-      </c>
-      <c r="C99" s="2">
-        <v>80</v>
+      <c r="B99" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>99</v>
       </c>
-      <c r="B100" s="2">
-        <v>90</v>
-      </c>
-      <c r="C100" s="2">
-        <v>81</v>
+      <c r="B100" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>100</v>
       </c>
-      <c r="B101" s="2">
-        <v>91</v>
-      </c>
-      <c r="C101" s="2">
-        <v>81</v>
+      <c r="B101" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>101</v>
       </c>
-      <c r="B102" s="2">
-        <v>91</v>
-      </c>
-      <c r="C102" s="2">
-        <v>12</v>
+      <c r="B102" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>102</v>
       </c>
-      <c r="B103" s="2">
-        <v>92</v>
-      </c>
-      <c r="C103" s="2">
-        <v>83</v>
+      <c r="B103" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>103</v>
       </c>
-      <c r="B104" s="2">
-        <v>93</v>
-      </c>
-      <c r="C104" s="2">
-        <v>82</v>
+      <c r="B104" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>104</v>
       </c>
-      <c r="B105" s="2">
-        <v>94</v>
-      </c>
-      <c r="C105" s="2">
-        <v>84</v>
+      <c r="B105" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>105</v>
       </c>
-      <c r="B106" s="2">
-        <v>95</v>
-      </c>
-      <c r="C106" s="2">
-        <v>85</v>
+      <c r="B106" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>106</v>
       </c>
-      <c r="B107" s="2">
-        <v>96</v>
-      </c>
-      <c r="C107" s="2">
-        <v>86</v>
+      <c r="B107" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>107</v>
       </c>
-      <c r="B108" s="2">
-        <v>97</v>
-      </c>
-      <c r="C108" s="2">
-        <v>87</v>
+      <c r="B108" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>108</v>
       </c>
-      <c r="B109" s="2">
-        <v>98</v>
-      </c>
-      <c r="C109" s="2">
-        <v>88</v>
+      <c r="B109" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>109</v>
       </c>
-      <c r="B110" s="2">
-        <v>99</v>
-      </c>
-      <c r="C110" s="2">
-        <v>89</v>
+      <c r="B110" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
